--- a/src/test/resources/MasterTestData - Copy.xlsx
+++ b/src/test/resources/MasterTestData - Copy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -753,7 +753,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1062,7 +1062,7 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="22.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="35.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="11.2190476190476" customWidth="1"/>
     <col min="4" max="4" width="14.4380952380952" customWidth="1"/>
